--- a/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>使生物生長修補的是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>細胞分裂</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>逐代倍增異常</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>增殖</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>攜帶遺傳物質的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>生長</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>與母細胞相同</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>染色體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>核內</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>染色體位於細胞的？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>細胞分裂</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>細胞核</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>生長</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>核</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>體細胞進行的分裂是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>體細胞</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>有絲分裂</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>生長</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>形成生殖細胞的分裂是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>減數分裂</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>一半</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>精卵</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>有絲分裂子細胞染色體數？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>與母細胞相同</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>生殖細胞</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>不變</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>減數分裂染色體數？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>減半</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>細胞分裂</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>與母細胞相同</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>一半</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>傷口癒合靠哪種分裂？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>有絲分裂</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>兩個子細胞</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>一半</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>修補</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>細胞分裂使生物體？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>生長</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>增殖</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>人體體細胞染色體有幾對？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>體細胞</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>使兩子細胞各得完整一套</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>23對</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>46條</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>有絲分裂一個母細胞分成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>兩個子細胞</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>與母細胞相同</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>二分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>減數分裂目的是形成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>生殖細胞</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>精卵</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>為何生殖細胞染色體要減半？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>確保子細胞獲得完整遺傳訊息</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>受精後恢復正常數</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>恢復</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>染色體在分裂前會？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>生長</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>體細胞</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>複製</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>倍增</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>精子與卵結合稱？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>受精</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>細胞分裂</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>有絲分裂用於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>細胞分裂</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>兩個子細胞</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>生長與修補</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>增生</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>人體體細胞染色體數受精後如何維持？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>使兩子細胞各得完整一套</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>精卵各半合成完整</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>染色體攜帶遺傳物質決定性狀</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>減數分裂發生在什麼細胞？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>使兩子細胞各得完整一套</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>精卵各半合成完整</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>確保子細胞獲得完整遺傳訊息</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>生殖細胞形成過程</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>生殖</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>有絲分裂常見於哪類細胞？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>與母細胞相同</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>體細胞</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>體細胞</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>減數分裂後染色體數變為原來的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>有絲分裂</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>一半</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>減半</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物5-1 細胞分裂　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>比較有絲分裂與減數分裂的染色體變化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>染色體攜帶遺傳物質決定性狀</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>受精後恢復正常數</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>有絲數目不變、減數減半</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何減數分裂能維持世代染色體數目恆定？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>生殖細胞形成過程</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>生殖細胞減半受精後恢復</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>染色體攜帶遺傳物質決定性狀</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>恆定</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>說明細胞分裂在生物中的三大用途？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞形成過程</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>精卵各半合成完整</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>世代染色體數目倍增異常</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>生長修補與生殖</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>染色體複製對正確分配的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>確保子細胞獲得完整遺傳訊息</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>世代染色體數目倍增異常</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>受精後恢復正常數</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>複製</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>若生殖細胞不減半會如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>使兩子細胞各得完整一套</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>世代染色體數目倍增異常</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>染色體攜帶遺傳物質決定性狀</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>後果</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>傷口癒合與胚胎發育共同依賴？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>有絲分裂增生細胞</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>受精後恢復正常數</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>共通</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>染色體與遺傳的關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>精卵各半合成完整</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>受精後恢復正常數</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>染色體攜帶遺傳物質決定性狀</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>關係</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>有絲分裂確保子細胞遺傳訊息如何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>生長</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>與母細胞相同</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>細胞核</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>一半</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何體細胞分裂要先複製染色體？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>使兩子細胞各得完整一套</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>生殖細胞減半受精後恢復</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>生殖細胞形成過程</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>生長修補與生殖</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>複製</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>若精卵不減半世代染色體會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>生殖細胞</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>染色體</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>逐代倍增異常</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>減數分裂</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>後果</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>增殖</t>
+          <t>增殖修補：細胞不斷分裂增加數量，讓生物體能夠長大並修補受傷的組織</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>核內</t>
+          <t>遺傳物質：染色體上帶有控制生物特徵的遺傳物質，會在分裂時傳給子細胞</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>核</t>
+          <t>位置：染色體平時位於細胞核內，分裂時才會變得明顯可見</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>生長</t>
+          <t>有絲分裂：一般的體細胞是靠有絲分裂增加數量，用來生長與修補組織</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>精卵</t>
+          <t>減數分裂：精子和卵這類生殖細胞，是經由減數分裂形成的</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>數目不變：有絲分裂後產生的子細胞，染色體數目和原本的母細胞完全相同</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>一半</t>
+          <t>數目減半：減數分裂會讓子細胞的染色體數目變成母細胞的一半</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>修補</t>
+          <t>修補傷口：傷口癒合是靠細胞不斷進行有絲分裂，增生出新細胞來修補</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>增殖</t>
+          <t>增殖：細胞經由分裂增加數目，是生物體生長發育的基礎</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>46條</t>
+          <t>46條：人體一般體細胞內含有23對、共46條染色體</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>二分</t>
+          <t>一分為二：有絲分裂時，一個母細胞會平均分裂成兩個染色體數相同的子細胞</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>精卵</t>
+          <t>形成精卵：減數分裂的目的是產生染色體數目減半的精子與卵等生殖細胞</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>恢復</t>
+          <t>恢復正常：精卵染色體數目各為一半，受精結合後才能剛好恢復成正常的數目</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>倍增</t>
+          <t>先複製：細胞分裂前染色體會先複製一份，之後才能平均分配給兩個子細胞</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>結合過程：精子與卵結合成受精卵的過程，稱為受精</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>增生</t>
+          <t>用途：有絲分裂主要用於讓生物體長大，以及修補受損的組織</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>維持</t>
+          <t>各半合成：精子與卵各帶一半染色體，受精結合後就能組成完整正常的染色體數目</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>生殖</t>
+          <t>形成過程：減數分裂發生在精子和卵這些生殖細胞形成的過程中</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>體細胞</t>
+          <t>體細胞：有絲分裂發生在體細胞，用來增加細胞數目、進行生長和修補，分裂後染色體數目不變</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>減半</t>
+          <t>減半：減數分裂會使產生的生殖細胞（精子、卵）染色體數目減半，這樣受精後才能恢復成原本的染色體數目</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>兩相對照：有絲分裂子細胞染色體數目和母細胞一樣，減數分裂則會讓數目減少一半</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>恆定</t>
+          <t>世代恆定：生殖細胞先減半，受精時精卵結合又剛好恢復原本數目，數目才不會越變越多</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>用途</t>
+          <t>三大用途：細胞分裂能讓生物體長大、修補受傷組織，也能用來產生生殖細胞繁衍後代</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>複製</t>
+          <t>完整遺傳：染色體先複製好，分裂時才能讓每個子細胞都拿到一份完整的遺傳訊息</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>後果</t>
+          <t>數目異常：如果生殖細胞染色體沒有減半，受精後染色體數目會一代一代不斷加倍造成異常</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>共同機制：傷口癒合和胚胎發育都需要細胞不斷靠有絲分裂增生，才能長出更多新細胞</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>關係</t>
+          <t>遺傳關係：染色體上帶著遺傳物質，這些物質決定了生物表現出來的各種性狀</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>訊息一致：有絲分裂能確保產生的子細胞，遺傳訊息和原本的母細胞完全一致</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>複製</t>
+          <t>複製：細胞分裂前必須先把染色體複製一份，這樣分裂後產生的兩個子細胞才能各自獲得一套完整的染色體，維持遺傳訊息不變</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>後果</t>
+          <t>後果：如果生殖細胞形成時染色體數目不減半，受精後染色體數目會加倍，一代一代下去染色體數目會不斷倍增，造成遺傳異常</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-1_三種難度測驗卷.xlsx
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>細胞核</t>
+          <t>一半</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>減數分裂</t>
+          <t>染色體</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>有絲分裂</t>
+          <t>逐代倍增異常</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>體細胞</t>
+          <t>細胞核</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>細胞分裂</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>減數分裂</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>使兩子細胞各得完整一套</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>細胞分裂</t>
+          <t>染色體</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>兩個子細胞</t>
+          <t>生殖細胞</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>有絲分裂</t>
+          <t>細胞核</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
